--- a/output/topology_excel/11784.xlsx
+++ b/output/topology_excel/11784.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B21" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B23" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B24" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B25" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B27" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B28" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B29" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B31" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B32" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B34" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B36" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F37" t="n">
-        <v>17</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38">
@@ -1257,7 +1257,7 @@
         <v>1</v>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,19 +1268,19 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>617</v>
+        <v>124</v>
       </c>
       <c r="F38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="n">
         <v>2</v>
       </c>
-      <c r="B39" t="n">
-        <v>3</v>
-      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1290,10 +1290,10 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="F39" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
@@ -1301,7 +1301,7 @@
         <v>2</v>
       </c>
       <c r="B40" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="F40" t="n">
-        <v>142</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
@@ -1323,7 +1323,7 @@
         <v>2</v>
       </c>
       <c r="B41" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>473</v>
+        <v>113</v>
       </c>
       <c r="F41" t="n">
         <v>18</v>
@@ -1345,7 +1345,7 @@
         <v>2</v>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>680</v>
+        <v>132</v>
       </c>
       <c r="F42" t="n">
         <v>17</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="F43" t="n">
-        <v>187</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B44" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="F44" t="n">
         <v>18</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B45" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="F45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B46" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,18 +1444,18 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="F46" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>395</v>
+        <v>128</v>
       </c>
       <c r="F47" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>617</v>
+        <v>128</v>
       </c>
       <c r="F48" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -1499,7 +1499,7 @@
         <v>4</v>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,18 +1510,18 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="F49" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B50" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,18 +1532,18 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="F50" t="n">
-        <v>167</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B51" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,10 +1554,10 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>253</v>
+        <v>128</v>
       </c>
       <c r="F51" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
@@ -1565,7 +1565,7 @@
         <v>5</v>
       </c>
       <c r="B52" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F52" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53">
@@ -1587,7 +1587,7 @@
         <v>6</v>
       </c>
       <c r="B53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F53" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
@@ -1609,7 +1609,7 @@
         <v>6</v>
       </c>
       <c r="B54" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="F54" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,10 +1642,10 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="F55" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
@@ -1653,7 +1653,7 @@
         <v>7</v>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="F56" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
@@ -1675,7 +1675,7 @@
         <v>7</v>
       </c>
       <c r="B57" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,18 +1686,18 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="F57" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B58" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,18 +1708,18 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>132</v>
+        <v>231</v>
       </c>
       <c r="F58" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B59" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,18 +1730,18 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F59" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B60" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,18 +1752,18 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>593</v>
+        <v>258</v>
       </c>
       <c r="F60" t="n">
-        <v>413</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B61" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1774,18 +1774,18 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>165</v>
+        <v>258</v>
       </c>
       <c r="F61" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B62" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,18 +1796,18 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="F62" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B63" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,18 +1818,18 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="F63" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B64" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1840,18 +1840,18 @@
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="F64" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B65" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1862,18 +1862,18 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="F65" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B66" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1884,40 +1884,40 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>418</v>
+        <v>204</v>
       </c>
       <c r="F66" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B67" t="n">
+        <v>29</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>137</v>
+      </c>
+      <c r="F67" t="n">
         <v>21</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
-        <v>586</v>
-      </c>
-      <c r="F67" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1928,18 +1928,18 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>143</v>
+        <v>256</v>
       </c>
       <c r="F68" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1950,19 +1950,19 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="F69" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
+        <v>11</v>
+      </c>
+      <c r="B70" t="n">
         <v>12</v>
       </c>
-      <c r="B70" t="n">
-        <v>24</v>
-      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1972,18 +1972,18 @@
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>870</v>
+        <v>104</v>
       </c>
       <c r="F70" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B71" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1994,18 +1994,18 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F71" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B72" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2016,18 +2016,18 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>235</v>
+        <v>104</v>
       </c>
       <c r="F72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B73" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="F73" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74">
@@ -2049,7 +2049,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2060,18 +2060,18 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>165</v>
+        <v>870</v>
       </c>
       <c r="F74" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B75" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>128</v>
+        <v>233</v>
       </c>
       <c r="F75" t="n">
         <v>24</v>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B76" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -2104,18 +2104,18 @@
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="F76" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B77" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2126,40 +2126,40 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="F77" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B78" t="n">
+        <v>34</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>97</v>
+      </c>
+      <c r="F78" t="n">
         <v>19</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" t="n">
-        <v>161</v>
-      </c>
-      <c r="F78" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B79" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2170,62 +2170,62 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="F79" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
+        <v>14</v>
+      </c>
+      <c r="B80" t="n">
+        <v>36</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>97</v>
+      </c>
+      <c r="F80" t="n">
         <v>19</v>
-      </c>
-      <c r="B80" t="n">
-        <v>20</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" t="n">
-        <v>612</v>
-      </c>
-      <c r="F80" t="n">
-        <v>407</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
+        <v>14</v>
+      </c>
+      <c r="B81" t="n">
+        <v>37</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>108</v>
+      </c>
+      <c r="F81" t="n">
         <v>19</v>
-      </c>
-      <c r="B81" t="n">
-        <v>25</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" t="n">
-        <v>204</v>
-      </c>
-      <c r="F81" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B82" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2236,18 +2236,18 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>510</v>
+        <v>152</v>
       </c>
       <c r="F82" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B83" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2258,18 +2258,18 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>137</v>
+        <v>617</v>
       </c>
       <c r="F83" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B84" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2280,18 +2280,18 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>256</v>
+        <v>151</v>
       </c>
       <c r="F84" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B85" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2302,18 +2302,18 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>231</v>
+        <v>473</v>
       </c>
       <c r="F85" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B86" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2324,18 +2324,18 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>258</v>
+        <v>680</v>
       </c>
       <c r="F86" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B87" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2346,18 +2346,18 @@
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>620</v>
+        <v>197</v>
       </c>
       <c r="F87" t="n">
-        <v>23</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B88" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2368,19 +2368,19 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>231</v>
+        <v>150</v>
       </c>
       <c r="F88" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
+        <v>16</v>
+      </c>
+      <c r="B89" t="n">
         <v>22</v>
       </c>
-      <c r="B89" t="n">
-        <v>26</v>
-      </c>
       <c r="C89" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -2390,18 +2390,18 @@
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>143</v>
+        <v>395</v>
       </c>
       <c r="F89" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B90" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2412,18 +2412,18 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>233</v>
+        <v>617</v>
       </c>
       <c r="F90" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B91" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2434,18 +2434,18 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="F91" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B92" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2456,18 +2456,18 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>258</v>
+        <v>187</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B93" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2478,18 +2478,18 @@
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>137</v>
+        <v>253</v>
       </c>
       <c r="F93" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B94" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2500,18 +2500,18 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="F94" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B95" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>112</v>
+        <v>253</v>
       </c>
       <c r="F95" t="n">
         <v>18</v>
@@ -2530,11 +2530,11 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
+        <v>23</v>
+      </c>
+      <c r="B96" t="n">
         <v>24</v>
       </c>
-      <c r="B96" t="n">
-        <v>27</v>
-      </c>
       <c r="C96" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -2544,18 +2544,18 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>277</v>
+        <v>593</v>
       </c>
       <c r="F96" t="n">
-        <v>19</v>
+        <v>413</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B97" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2566,18 +2566,18 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="F97" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B98" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2588,18 +2588,18 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>97</v>
+        <v>591</v>
       </c>
       <c r="F98" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B99" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2610,18 +2610,18 @@
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>94</v>
+        <v>418</v>
       </c>
       <c r="F99" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B100" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2632,18 +2632,18 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>97</v>
+        <v>394</v>
       </c>
       <c r="F100" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B101" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2654,19 +2654,19 @@
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F101" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
+        <v>24</v>
+      </c>
+      <c r="B102" t="n">
         <v>26</v>
       </c>
-      <c r="B102" t="n">
-        <v>34</v>
-      </c>
       <c r="C102" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -2676,19 +2676,19 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>116</v>
+        <v>235</v>
       </c>
       <c r="F102" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
+        <v>26</v>
+      </c>
+      <c r="B103" t="n">
         <v>27</v>
       </c>
-      <c r="B103" t="n">
-        <v>28</v>
-      </c>
       <c r="C103" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -2698,18 +2698,18 @@
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F103" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B104" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2720,18 +2720,18 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>297</v>
+        <v>612</v>
       </c>
       <c r="F104" t="n">
-        <v>135</v>
+        <v>407</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B105" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2742,18 +2742,18 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>123</v>
+        <v>304</v>
       </c>
       <c r="F105" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B106" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2764,18 +2764,18 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>105</v>
+        <v>258</v>
       </c>
       <c r="F106" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B107" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2786,15 +2786,15 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="F107" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B108" t="n">
         <v>33</v>
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="F108" t="n">
         <v>20</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B109" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2830,18 +2830,18 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>123</v>
+        <v>297</v>
       </c>
       <c r="F109" t="n">
-        <v>18</v>
+        <v>135</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B110" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2852,18 +2852,18 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="F110" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B111" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2874,18 +2874,18 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F111" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B112" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2896,18 +2896,18 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="F112" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B113" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F113" t="n">
         <v>20</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B114" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2940,18 +2940,18 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="F114" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B115" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2962,10 +2962,1110 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F115" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>36</v>
+      </c>
+      <c r="B116" t="n">
+        <v>37</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>123</v>
+      </c>
+      <c r="F116" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>36</v>
+      </c>
+      <c r="B117" t="n">
+        <v>38</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>97</v>
+      </c>
+      <c r="F117" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>37</v>
+      </c>
+      <c r="B118" t="n">
+        <v>38</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>108</v>
+      </c>
+      <c r="F118" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>13</v>
+      </c>
+      <c r="B119" t="n">
+        <v>25</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>236</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>13</v>
+      </c>
+      <c r="B120" t="n">
+        <v>27</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>236</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>9</v>
+      </c>
+      <c r="B121" t="n">
+        <v>30</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>260</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>9</v>
+      </c>
+      <c r="B122" t="n">
+        <v>30</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>9</v>
+      </c>
+      <c r="B123" t="n">
+        <v>30</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>9</v>
+      </c>
+      <c r="B124" t="n">
+        <v>30</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>9</v>
+      </c>
+      <c r="B125" t="n">
+        <v>30</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>9</v>
+      </c>
+      <c r="B126" t="n">
+        <v>30</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>9</v>
+      </c>
+      <c r="B127" t="n">
+        <v>30</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>9</v>
+      </c>
+      <c r="B128" t="n">
+        <v>30</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>9</v>
+      </c>
+      <c r="B129" t="n">
+        <v>30</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>9</v>
+      </c>
+      <c r="B130" t="n">
+        <v>30</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>9</v>
+      </c>
+      <c r="B131" t="n">
+        <v>30</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>9</v>
+      </c>
+      <c r="B132" t="n">
+        <v>30</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>9</v>
+      </c>
+      <c r="B133" t="n">
+        <v>30</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>9</v>
+      </c>
+      <c r="B134" t="n">
+        <v>30</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>9</v>
+      </c>
+      <c r="B135" t="n">
+        <v>30</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>9</v>
+      </c>
+      <c r="B136" t="n">
+        <v>30</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>9</v>
+      </c>
+      <c r="B137" t="n">
+        <v>30</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>9</v>
+      </c>
+      <c r="B138" t="n">
+        <v>30</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>9</v>
+      </c>
+      <c r="B139" t="n">
+        <v>30</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>9</v>
+      </c>
+      <c r="B140" t="n">
+        <v>30</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>9</v>
+      </c>
+      <c r="B141" t="n">
+        <v>30</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>9</v>
+      </c>
+      <c r="B142" t="n">
+        <v>30</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>9</v>
+      </c>
+      <c r="B143" t="n">
+        <v>30</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>9</v>
+      </c>
+      <c r="B144" t="n">
+        <v>30</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>9</v>
+      </c>
+      <c r="B145" t="n">
+        <v>30</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>9</v>
+      </c>
+      <c r="B146" t="n">
+        <v>30</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>9</v>
+      </c>
+      <c r="B147" t="n">
+        <v>30</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>9</v>
+      </c>
+      <c r="B148" t="n">
+        <v>30</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>9</v>
+      </c>
+      <c r="B149" t="n">
+        <v>30</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>9</v>
+      </c>
+      <c r="B150" t="n">
+        <v>30</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>9</v>
+      </c>
+      <c r="B151" t="n">
+        <v>30</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>9</v>
+      </c>
+      <c r="B152" t="n">
+        <v>30</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>9</v>
+      </c>
+      <c r="B153" t="n">
+        <v>30</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>9</v>
+      </c>
+      <c r="B154" t="n">
+        <v>30</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>9</v>
+      </c>
+      <c r="B155" t="n">
+        <v>30</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>9</v>
+      </c>
+      <c r="B156" t="n">
+        <v>30</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>9</v>
+      </c>
+      <c r="B157" t="n">
+        <v>30</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>9</v>
+      </c>
+      <c r="B158" t="n">
+        <v>30</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>9</v>
+      </c>
+      <c r="B159" t="n">
+        <v>30</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>9</v>
+      </c>
+      <c r="B160" t="n">
+        <v>30</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>9</v>
+      </c>
+      <c r="B161" t="n">
+        <v>30</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>9</v>
+      </c>
+      <c r="B162" t="n">
+        <v>30</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>9</v>
+      </c>
+      <c r="B163" t="n">
+        <v>30</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>9</v>
+      </c>
+      <c r="B164" t="n">
+        <v>30</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>9</v>
+      </c>
+      <c r="B165" t="n">
+        <v>30</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>349</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
